--- a/output/第10期計画_令和8年8月28日受領資料の点検結果.xlsx
+++ b/output/第10期計画_令和8年8月28日受領資料の点検結果.xlsx
@@ -981,7 +981,7 @@
         <is>
           <t>注1）本点検は受領資料の内容の確認であり、計画本文への反映は03シートに掲げる箇所について順次行います。
 注2）医療機関リスト・薬局リストは北海道全域のデータです。区域内の抽出と、介護サービス情報公表システムの事業所一覧との突合は別途行います。
-注3）令和8年8月25日の打合せでご依頼した年報・月報（資料No.21・22）及び給付実績データ（同No.23）は、本受領には含まれていません。</t>
+注3）令和8年8月26日の打合せでご依頼した年報・月報（資料No.21・22）及び給付実績データ（同No.23）は、本受領には含まれていません。</t>
         </is>
       </c>
     </row>
